--- a/docs/revised_shatin/qwen3-next-80b-a3b-thinking/test_grammar_2_['No. 91_～ば〈条件(じょうけん)〉 ']_revised_revised.xlsx
+++ b/docs/revised_shatin/qwen3-next-80b-a3b-thinking/test_grammar_2_['No. 91_～ば〈条件(じょうけん)〉 ']_revised_revised.xlsx
@@ -467,12 +467,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 お金があれば、(   )。</t>
+          <t>: もんだい1 お金があれば、(   )。</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>1. 新しいパソコンを買います 2. 旅行に行きます 3. お金を貯めます 4. お酒を飲みます</t>
+          <t>1. 買い物に行きます 2. 友だちと遊びます 3. 家にいます 4. 勉強します</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -491,12 +491,12 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 時間があれば、(   )。</t>
+          <t>: もんだい1 時間があれば、(   )。</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1. 本を読みます 2. 仕事をします 3. 遅刻します 4. 病気になります</t>
+          <t>1. 手伝いましょう 2. 休みましょう 3. 急ぎましょう 4. 帰りましょう</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 この道をまっすぐ行けば、(   )。</t>
+          <t>: もんだい1 この道をまっすぐ行けば、(   )。</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 いい天気ならば、(   )。</t>
+          <t>: もんだい1 いい天気ならば、(   )。</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>1. パーティーをします 2. 家で勉強します 3. 早く寝ます 4. 仕事に行きます</t>
+          <t>1. 外でピクニックをします 2. 家で本を読みます 3. 早く寝ます 4. 映画を見ます</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 彼が来れば、(   )。</t>
+          <t>: もんだい1 彼が来れば、(   )。</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>1. ケーキを食べます 2. みんな帰ります 3. 何もしません 4. 電話します</t>
+          <t>1. パーティーを始めます 2. みんな帰ります 3. 終わります 4. 片付けます</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 安ければ、(   )。</t>
+          <t>: もんだい1 安ければ、(   )。</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>1. 買います 2. 売ります 3. 捨てます 4. しまいます</t>
+          <t>1. 買いたいです 2. 売りたいです 3. 借りたいです 4. 捨てたいです</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 早く起きれば、(   )。</t>
+          <t>: もんだい1 早く起きれば、(   )。</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>1. 朝ごはんを食べます 2. 遅刻します 3. 寝坊します 4. 忘れ物をします</t>
+          <t>1. 朝ごはんを作れます 2. 遅刻します 3. 寝坊します 4. 忘れ物をします</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 日本語が上手になれば、(   )。</t>
+          <t>: もんだい1 日本語が上手になれば、(   )。</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>1. 日本で働けます 2. 日本から帰ります 3. 日本へ行きません 4. 日本語をやめます</t>
+          <t>1. 日本で働きたいです 2. 日本から帰ります 3. 日本へ行きません 4. 日本語をやめます</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 勉強すれば、(   )。</t>
+          <t>: もんだい1 勉強すれば、(   )。</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -683,20 +683,20 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 昨日、友達（ ）会いました。</t>
+          <t>: もんだい2 雨が降れば、試合は中止(   )。</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>1. で
-2. に
-3. と
-4. へ</t>
+          <t>1. になる
+2. する
+3. したい
+4. ある</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr"/>
@@ -705,17 +705,17 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 時間が あれば 本を (   )。</t>
+          <t>: もんだい2 時間があれば、本を(   )。</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>1. 読む 2. 書く 3. 見る 4. 作る</t>
+          <t>1. 読みたい 2. 読む 3. 読んで 4. 読まない</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
@@ -729,17 +729,17 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Q12</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 お金を ためれば 新しい パソコンを (   )。</t>
+          <t>: もんだい2 お金をためれば、新しいパソコンを(   )。</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>1. 買う 2. 売る 3. 借りる 4. 使う</t>
+          <t>1. 買いたい 2. 買う 3. 買って 4. 買わない</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
@@ -753,17 +753,17 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 早く 寝れば 朝 元気に (   )。</t>
+          <t>: もんだい2 早く寝れば、朝元気に(   )。</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1. 起きる 2. 寝る 3. 食べる 4. 行く</t>
+          <t>1. 起きられる 2. 起きる 3. 起きない 4. 起きて</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
@@ -777,17 +777,17 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Q14</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 仕事が 終われば 友達と (   )。</t>
+          <t>: もんだい2 仕事が終われば、友達と(   )。</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>1. 遊ぶ 2. 学ぶ 3. 泳ぐ 4. 働く</t>
+          <t>1. 遊びたい 2. 遊ぶ 3. 遊んで 4. 遊ばない</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
@@ -801,17 +801,17 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Q15</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 天気が 良ければ ピクニックに (   )。</t>
+          <t>: もんだい2 天気が良ければ、ピクニックに(   )。</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>1. 行く 2. 帰る 3. 来る 4. 戻る</t>
+          <t>1. 行きたい 2. 行く 3. 行って 4. 行かない</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
@@ -825,17 +825,17 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Q16</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 暇が あれば 映画を (   )。</t>
+          <t>: もんだい2 暇があれば、映画を(   )。</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>1. 見る 2. 聞く 3. 話す 4. 描く</t>
+          <t>1. 見たい 2. 見る 3. 見て 4. 見ない</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
@@ -849,17 +849,17 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Q17</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 時間が あれば、手伝いに (   )。</t>
+          <t>: もんだい2 時間があれば、手伝いに(   )。</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>1. 行く 2. 寝る 3. 立つ 4. 走る</t>
+          <t>1. 行きたい 2. 行く 3. 行って 4. 行かない</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
@@ -873,17 +873,17 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Q18</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 勉強すれば、試験に (   )。</t>
+          <t>: もんだい2 勉強すれば、試験に(   )。</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>1. 合格する 2. 失敗する 3. 落ちる 4. 終わる</t>
+          <t>1. 合格したい 2. 合格する 3. 合格して 4. 合格しない</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
@@ -897,17 +897,17 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Q19</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 お金が あれば、旅行に (   )。</t>
+          <t>: もんだい2 お金があれば、旅行に(   )。</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>1. 行く 2. 泊まる 3. 走る 4. 飛ぶ</t>
+          <t>1. 行きたい 2. 行く 3. 行って 4. 行かない</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
@@ -921,22 +921,22 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Q20</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 雨が降れば、試合は(   )。</t>
+          <t>: もんだい3 雨が降れば、試合は(   )。</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>1. 中止だ 2. 中止にする 3. 中止で 4. 中止になる</t>
+          <t>1. 中止になる 2. 中止する 3. 中止で 4. 中止したい</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr"/>
@@ -945,12 +945,12 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Q21</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 この薬を飲めば、すぐに(   )。</t>
+          <t>: もんだい3 この薬を飲めば、すぐに(   )。</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -969,17 +969,17 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Q22</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 時間があれば、映画を(   )。</t>
+          <t>: もんだい3 時間があれば、映画を(   )。</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>1. 見る 2. 見て 3. 見ます 4. 見ない</t>
+          <t>1. 見たい 2. 見て 3. 見ます 4. 見ない</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
@@ -993,17 +993,17 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Q23</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 お金があれば、あの車を(   )。</t>
+          <t>: もんだい3 お金があれば、あの車を(   )。</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>1. 買う 2. 買いました 3. 買って 4. 買わない</t>
+          <t>1. 買いたい 2. 買いました 3. 買って 4. 買わない</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
@@ -1017,12 +1017,12 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Q24</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 友達が来れば、パーティーがもっと(   )。</t>
+          <t>: もんだい3 友達が来れば、パーティーがもっと(   )。</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Q25</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 天気が良ければ、ピクニックに(   )。</t>
+          <t>: もんだい3 天気が良ければ、ピクニックに(   )。</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>1. 行く 2. 行って 3. 行かない 4. 行こう</t>
+          <t>1. 行きたい 2. 行って 3. 行かない 4. 行こう</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
@@ -1065,17 +1065,17 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Q26</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 もっと勉強すれば、試験に(   )。</t>
+          <t>: もんだい3 もっと勉強すれば、試験に(   )。</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>1. 合格する 2. 合格して 3. 合格しない 4. 合格だ</t>
+          <t>1. 合格したい 2. 合格して 3. 合格しない 4. 合格だ</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
@@ -1089,20 +1089,17 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Q27</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 静かにすれば、赤ちゃんが（ ）。</t>
+          <t>: もんだい3 静かにすれば、赤ちゃんが(   )。</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>1. 眠ります
-2. 眠って
-3. 眠らない
-4. 眠い</t>
+          <t>1. 眠る 2. 眠って 3. 眠らない 4. 眠い</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
@@ -1116,12 +1113,12 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Q28</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 運動すれば、健康が(   )。</t>
+          <t>: もんだい3 運動すれば、健康が(   )。</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
@@ -1140,12 +1137,12 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Q29</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 早く寝れば、朝早く(   )。</t>
+          <t>: もんだい3 早く寝れば、朝早く(   )。</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
@@ -1164,17 +1161,17 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Q30</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 雨が 降れば、 ピクニックは (   ).</t>
+          <t>: もんだい4 もし雨が降れば、ピクニックは(   )。</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>1. 中止したい 2. 中止する 3. 中止しよう 4. 中止した</t>
+          <t>1. 中止したい 2. 中止しよう 3. 中止する 4. 中止した</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
@@ -1188,17 +1185,17 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Q31</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 彼が 来れば、 映画を 一緒に (   ).</t>
+          <t>: もんだい4 彼が来れば、映画を一緒に(   )。</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>1. 見よう 2. 見たかった 3. 見たい 4. 見る</t>
+          <t>1. 見たい 2. 見たかった 3. 見たい 4. 見る</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
@@ -1212,22 +1209,22 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Q32</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 この薬を 飲めば、 すぐに (   ).</t>
+          <t>: もんだい4 この薬を飲めば、すぐに(   )。</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>1. よくなりたがる 2. よくなる 3. よくなっている 4. よくなりたい</t>
+          <t>1. よくなる 2. よくなりたがる 3. よくなっている 4. よくなりたい</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr"/>
@@ -1236,22 +1233,22 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Q33</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 試験に 合格すれば、 大学に (   ).</t>
+          <t>: もんだい4 もし試験に合格すれば、大学に(   )。</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>1. 行くことにした 2. 行きたかった 3. 行くつもりだ 4. 行こうと思う</t>
+          <t>1. 行くつもりだ 2. 行きたかった 3. 行くことにした 4. 行こうと思う</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr"/>
@@ -1260,22 +1257,22 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Q34</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 時間が あれば、 あなたに 手紙を (   ).</t>
+          <t>: もんだい4 時間があれば、あなたに手紙を(   )。</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>1. 書く 2. 書くことにした 3. 書きたい 4. 書こうと思う</t>
+          <t>1. 書きたい 2. 書くことにした 3. 書く 4. 書こうと思う</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr"/>
@@ -1284,22 +1281,22 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Q35</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 彼女が 来れば、 一緒に (   ).</t>
+          <t>: もんだい4 もし彼女が来れば、一緒に(   )。</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>1. 夕食を 食べたい 2. 夕食を 食べたかった 3. 夕食を 食べよう 4. 夕食を 食べる</t>
+          <t>1. 夕食を食べよう 2. 夕食を食べたかった 3. 夕食を食べたい 4. 夕食を食べる</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr"/>
@@ -1308,22 +1305,22 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Q36</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 彼女が 手伝えば、 もっと 早く (   ).</t>
+          <t>: もんだい4 彼女が手伝えば、もっと早く(   )。</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>1. 終わらせたかった 2. 終わらせたい 3. 終わらせよう 4. 終わらせる</t>
+          <t>1. 終わらせたい 2. 終わらせよう 3. 終わらせる 4. 終わらせたかった</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr"/>
@@ -1332,17 +1329,17 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Q37</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし お金が あれば、 新しいスマホを (   ).</t>
+          <t>: もんだい4 もしお金があれば、新しいスマホを(   )。</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>1. 買いたい 2. 買う 3. 買おう 4. 買うことにした</t>
+          <t>1. 買いたい 2. 買おう 3. 買う 4. 買うことにした</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
@@ -1356,22 +1353,22 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Q38</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もっと 練習すれば、 試合に (   )。</t>
+          <t>: もんだい4 もっと練習すれば、試合に(   )。</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>1. 勝ちたがる 2. 勝てる 3. 勝ちたい 4. 勝ちそうだ</t>
+          <t>1. 勝てる 2. 勝ちたい 3. 勝ちたがる 4. 勝ちそうだ</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr"/>
@@ -1380,22 +1377,22 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Q39</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 これを やれば、 すぐに 終わると (   ).</t>
+          <t>: もんだい4 これをやれば、すぐに終わると(   )。</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>1. 思った 2. 思っている 3. 思いたい 4. 思う</t>
+          <t>1. 思う 2. 思った 3. 思いたい 4. 思っている</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr"/>
@@ -1404,12 +1401,12 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Q40</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 この本は面白いが、あの本 (   ) 面白くない。</t>
+          <t>: もんだい5 この本は面白いが、あの本(   )面白くない。</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -1419,7 +1416,7 @@
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr"/>
@@ -1428,12 +1425,12 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Q41</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 この道をまっすぐ行け (   ) 駅に着きますよ。</t>
+          <t>: もんだい5 この道をまっすぐ行けば、駅に着きますよ。</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -1452,12 +1449,12 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>Q42</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 雨が降らなけれ (   ) ピクニックに行きます。</t>
+          <t>: もんだい5 雨が降らなければ、ピクニックに行きます。</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -1476,12 +1473,12 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>Q43</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 宿題を終わらせれ (   ) 遊びに行ってもいいです。</t>
+          <t>: もんだい5 宿題を終わらせれば、遊びに行ってもいいです。</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -1500,25 +1497,22 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Q44</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>: もんだい10 この問題は（ ）難しいです。</t>
+          <t>: もんだい5 この映画は怖いが、あの映画(   )怖くない。</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>1. あまり
-2. とても
-3. あまりも
-4. あまりの</t>
+          <t>1. ほど 2. から 3. なら 4. まで</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr"/>
@@ -1527,20 +1521,17 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Q45</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>: もんだい11 学校に（ ）行きました。</t>
+          <t>: もんだい5 たくさん練習すれば、上手になります。</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>1. で
-2. に
-3. と
-4. へ</t>
+          <t>1. なら 2. ば 3. ほど 4. から</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
@@ -1554,25 +1545,22 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Q46</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>: もんだい12 この本は（ ）面白いです。</t>
+          <t>: もんだい5 お金があれば、旅行に行きたいです。</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>1. あまり
-2. とても
-3. あまりも
-4. あまりの</t>
+          <t>1. ば 2. から 3. ほど 4. しか</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr"/>
@@ -1581,20 +1569,17 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Q47</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>: もんだい13 彼は日本語を（ ）勉強しています。</t>
+          <t>: もんだい5 早く寝れば、明日元気になります。</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>1. 一生懸命
-2. 一生懸命の
-3. 一生懸命で
-4. 一生懸命に</t>
+          <t>1. ば 2. から 3. ほど 4. だけ</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
@@ -1608,25 +1593,22 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Q48</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>: もんだい14 このケーキは（ ）甘いです。</t>
+          <t>: もんだい5 彼は賢いが、彼女(   )賢くない。</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>1. あまり
-2. とても
-3. あまりも
-4. あまりの</t>
+          <t>1. ほど 2. ば 3. から 4. まで</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr"/>
@@ -1635,25 +1617,22 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Q49</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>: もんだい15 駅まで（ ）バスに乗ります。</t>
+          <t>: もんだい5 勉強すれば、するほど、試験が簡単になります。</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>1. いつも
-2. いつもの
-3. いつもで
-4. いつもに</t>
+          <t>1. なら 2. ば 3. ほど 4. から</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr"/>
@@ -1662,17 +1641,17 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Q50</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「雨が降れば、」 B:「(   )。 」</t>
+          <t>: もんだい6 A:「雨が降れば、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>1. 試合は中止です 2. 試合が中止です 3. 試合を中止です 4. 試合は中止にします</t>
+          <t>1. 試合は中止になる 2. 試合が中止になる 3. 試合を中止になる 4. 試合は中止にする</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
@@ -1686,25 +1665,22 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>Q51</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>: もんだい16 この映画は（ ）面白いです。</t>
+          <t>: もんだい6 A:「この本、面白ければ、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>1. あまり
-2. とても
-3. あまりも
-4. あまりの</t>
+          <t>1. 私に貸してくれませんか 2. 私に貸してください 3. 私に貸してもいいですか 4. 私に貸していただけますか</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr"/>
@@ -1713,25 +1689,22 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>Q52</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>: もんだい17 昨日、友達と（ ）映画を見ました。</t>
+          <t>: もんだい6 A:「時間があれば、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>1. で
-2. に
-3. と
-4. へ</t>
+          <t>1. 一緒に行きませんか 2. 一緒に行ってもいいですか 3. 一緒に行ってください 4. 一緒に行ってほしいです</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr"/>
@@ -1740,20 +1713,17 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>Q53</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>: もんだい18 この本は（ ）読みやすいです。</t>
+          <t>: もんだい6 A:「いい天気なら、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>1. とても
-2. あまり
-3. すごく
-4. たいへん</t>
+          <t>1. 山に登りましょう 2. 山に登ります 3. 山に登ってください 4. 山に登りたいです</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
@@ -1767,20 +1737,17 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>Q54</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>: もんだい19 この薬は一日（ ）飲みます。</t>
+          <t>: もんだい6 A:「もし暇があれば、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>1. 三回
-2. 三回の
-3. 三回で
-4. 三回に</t>
+          <t>1. 映画を見に行きましょうか 2. 映画を見に行ってください 3. 映画を見に行きますか 4. 映画を見に行ってもいいですか</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
@@ -1794,12 +1761,12 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>Q55</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「風邪を引いたら、」 B:「(   )。 」</t>
+          <t>: もんだい6 A:「風邪を引いたら、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -1818,12 +1785,12 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>Q56</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「道が分からなければ、」 B:「(   )。 」</t>
+          <t>: もんだい6 A:「道が分からなければ、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -1842,12 +1809,12 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>Q57</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「お金があれば、」 B:「(   )。 」</t>
+          <t>: もんだい6 A:「お金があれば、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -1866,12 +1833,12 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>Q58</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「疲れたら、」 B:「(   )。 」</t>
+          <t>: もんだい6 A:「疲れたら、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -1890,22 +1857,22 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>Q59</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「彼が来れば、」 B:「(   )。 」</t>
+          <t>: もんだい6 A:「彼が来れば、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>1. パーティーを始めます 2. パーティーを始めましょう 3. パーティーを始めてください 4. パーティーを始めてもいいですか</t>
+          <t>1. パーティーを始めましょう 2. パーティーを始めます 3. パーティーを始めてください 4. パーティーを始めてもいいですか</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr"/>
@@ -1914,22 +1881,22 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>Q60</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 雨が降れば、ピクニックは(   )。</t>
+          <t>: もんだい7 雨が降れば、ピクニックは(   )。</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>1. 中止にしよう 2. 中止になる 3. 中止にする 4. 中止できる</t>
+          <t>1. 中止になる 2. 中止にしよう 3. 中止する 4. 中止できる</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr"/>
@@ -1938,22 +1905,22 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>Q61</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 あの映画は面白ければ、(   )。</t>
+          <t>: もんだい7 あの映画は面白ければ、(   )。</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>1. 見ることになる 2. 見たくなる 3. 見なければならない 4. 見よう</t>
+          <t>1. 見たくなる 2. 見ることになる 3. 見なければならない 4. 見よう</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr"/>
@@ -1962,12 +1929,12 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>Q62</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 勉強すれば、テストに(   )。</t>
+          <t>: もんだい7 勉強すれば、テストに(   )。</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -1986,22 +1953,22 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>Q63</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 このボタンを押せば、(   )。</t>
+          <t>: もんだい7 このボタンを押せば、(   )。</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>1. ドアが開ける 2. ドアが開く 3. ドアを開ける 4. ドアを開かない</t>
+          <t>1. ドアが開く 2. ドアが開ける 3. ドアを開ける 4. ドアを開かない</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr"/>
@@ -2010,12 +1977,12 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>Q64</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 この薬を飲めば、(   )。</t>
+          <t>: もんだい7 この薬を飲めば、(   )。</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
@@ -2034,22 +2001,22 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>Q65</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 時間があれば、(   )。</t>
+          <t>: もんだい7 時間があれば、(   )。</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>1. 映画を見たい 2. 映画を見よう 3. 映画を見ようと思う 4. 映画を見てもいい</t>
+          <t>1. 映画を見よう 2. 映画を見たい 3. 映画を見ようと思う 4. 映画を見てもいい</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr"/>
@@ -2058,12 +2025,12 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>Q66</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 家に帰れば、(   )。</t>
+          <t>: もんだい7 家に帰れば、(   )。</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -2082,12 +2049,12 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>Q67</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 お金があれば、(   )。</t>
+          <t>: もんだい7 お金があれば、(   )。</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -2106,22 +2073,22 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>Q68</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 彼が来れば、(   )。</t>
+          <t>: もんだい7 彼が来れば、(   )。</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>1. パーティーが始める 2. パーティーを始める 3. パーティーが始まる 4. パーティーを始まる</t>
+          <t>1. パーティーが始まる 2. パーティーを始める 3. パーティーが始める 4. パーティーを始まる</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr"/>
@@ -2130,12 +2097,12 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>Q69</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 この本を読めば、(   )。</t>
+          <t>: もんだい7 この本を読めば、(   )。</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -2154,12 +2121,12 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>Q70</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 雨が降れば、道が(   )なる。</t>
+          <t>: もんだい8 雨が降れば、道が(   )なる。</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
@@ -2178,12 +2145,12 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>Q71</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 その子供は、大人の(   )賢い。</t>
+          <t>: もんだい8 その子供は、大人の(   )賢い。</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -2202,12 +2169,12 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>Q72</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 彼女が笑えば、太陽の(   )明るくなる。</t>
+          <t>: もんだい8 彼女が笑えば、太陽の(   )明るくなる。</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -2226,12 +2193,12 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>Q73</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 もし疲れれば、猫の(   )眠ることができる。</t>
+          <t>: もんだい8 もし疲れれば、猫の(   )眠ることができる。</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -2250,12 +2217,12 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>Q74</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 彼が来れば、すべてが(   )解決する。</t>
+          <t>: もんだい8 彼が来れば、すべてが(   )解決する。</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -2274,12 +2241,12 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>Q75</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 この歌を聴けば、昔の(   )思い出す。</t>
+          <t>: もんだい8 この歌を聴けば、昔の(   )思い出す。</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -2298,12 +2265,12 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>Q76</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 彼女が手伝えば、仕事が(   )早く終わる。</t>
+          <t>: もんだい8 彼女が手伝えば、仕事が(   )早く終わる。</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -2322,12 +2289,12 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>Q77</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 あの映画を見れば、夢の(   )感じる。</t>
+          <t>: もんだい8 あの映画を見れば、夢の(   )感じる。</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -2346,12 +2313,12 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>Q78</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 彼が説明すれば、子供でも(   )わかる。</t>
+          <t>: もんだい8 彼が説明すれば、子供でも(   )わかる。</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -2370,12 +2337,12 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>Q79</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 この薬を飲めば、魔法の(   )効く。</t>
+          <t>: もんだい8 この薬を飲めば、魔法の(   )効く。</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">

--- a/docs/revised_shatin/qwen3-next-80b-a3b-thinking/test_grammar_2_['No. 91_～ば〈条件(じょうけん)〉 ']_revised_revised.xlsx
+++ b/docs/revised_shatin/qwen3-next-80b-a3b-thinking/test_grammar_2_['No. 91_～ば〈条件(じょうけん)〉 ']_revised_revised.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -467,17 +467,17 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 お金があれば、(   )。</t>
+          <t>: もんだい1雨が降れば、(   )。</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>1. 買い物に行きます 2. 友だちと遊びます 3. 家にいます 4. 勉強します</t>
+          <t>1. うちに帰ります 2. 外で遊びます 3. 傘を持っていきます 4. 洗濯します</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr"/>
@@ -491,12 +491,12 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 時間があれば、(   )。</t>
+          <t>: もんだい1お金があれば、(   )。</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1. 手伝いましょう 2. 休みましょう 3. 急ぎましょう 4. 帰りましょう</t>
+          <t>1. 買い物に行きます 2. 友だちと遊びます 3. 家にいます 4. 勉強します</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -515,12 +515,12 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 この道をまっすぐ行けば、(   )。</t>
+          <t>: もんだい1時間があれば、(   )。</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>1. 駅に着きます 2. 迷います 3. 遠回りします 4. 戻ります</t>
+          <t>1. 手伝いましょう 2. 休みましょう 3. 急ぎましょう 4. 帰りましょう</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 いい天気ならば、(   )。</t>
+          <t>: もんだい1この道をまっすぐ行けば、(   )。</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>1. 外でピクニックをします 2. 家で本を読みます 3. 早く寝ます 4. 映画を見ます</t>
+          <t>1. 駅に着きます 2. 迷います 3. 遠回りします 4. 戻ります</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 彼が来れば、(   )。</t>
+          <t>: もんだい1いい天気ならば、(   )。</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>1. パーティーを始めます 2. みんな帰ります 3. 終わります 4. 片付けます</t>
+          <t>1. 外でピクニックをします 2. 家で本を読みます 3. 早く寝ます 4. 映画を見ます</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 安ければ、(   )。</t>
+          <t>: もんだい1彼が来れば、(   )。</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>1. 買いたいです 2. 売りたいです 3. 借りたいです 4. 捨てたいです</t>
+          <t>1. パーティーを始めます 2. みんな帰ります 3. 終わります 4. 片付けます</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 早く起きれば、(   )。</t>
+          <t>: もんだい1安ければ、(   )。</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>1. 朝ごはんを作れます 2. 遅刻します 3. 寝坊します 4. 忘れ物をします</t>
+          <t>1. 買いたいです 2. 売りたいです 3. 借りたいです 4. 捨てたいです</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 日本語が上手になれば、(   )。</t>
+          <t>: もんだい1早く起きれば、(   )。</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>1. 日本で働きたいです 2. 日本から帰ります 3. 日本へ行きません 4. 日本語をやめます</t>
+          <t>1. 朝ごはんを作れます 2. 遅刻します 3. 寝坊します 4. 忘れ物をします</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
@@ -659,12 +659,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 勉強すれば、(   )。</t>
+          <t>: もんだい1日本語が上手になれば、(   )。</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>1. テストに合格できます 2. テストに落ちます 3. テストを忘れます 4. テストをしません</t>
+          <t>1. 日本で働きたいです 2. 日本から帰ります 3. 日本へ行きません 4. 日本語をやめます</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
@@ -683,20 +683,17 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2 雨が降れば、試合は中止(   )。</t>
+          <t>: もんだい1勉強すれば、(   )。</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>1. になる
-2. する
-3. したい
-4. ある</t>
+          <t>1. テストに合格できます 2. テストに落ちます 3. テストを忘れます 4. テストをしません</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr"/>
@@ -710,12 +707,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2 時間があれば、本を(   )。</t>
+          <t>: もんだい2雨が 降れば 試合は 中止に (   )。</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>1. 読みたい 2. 読む 3. 読んで 4. 読まない</t>
+          <t>1. なる 2. する 3. いる 4. ある</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
@@ -734,12 +731,12 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2 お金をためれば、新しいパソコンを(   )。</t>
+          <t>: もんだい2時間が あれば 本を (   )。</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>1. 買いたい 2. 買う 3. 買って 4. 買わない</t>
+          <t>1. 読む 2. 書く 3. 見る 4. 作る</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
@@ -758,12 +755,12 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2 早く寝れば、朝元気に(   )。</t>
+          <t>: もんだい2お金を ためれば 新しい パソコンを (   )。</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1. 起きられる 2. 起きる 3. 起きない 4. 起きて</t>
+          <t>1. 買う 2. 売る 3. 借りる 4. 使う</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
@@ -782,12 +779,12 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2 仕事が終われば、友達と(   )。</t>
+          <t>: もんだい2早く 寝れば 朝 元気に (   )。</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>1. 遊びたい 2. 遊ぶ 3. 遊んで 4. 遊ばない</t>
+          <t>1. 起きる 2. 寝る 3. 食べる 4. 行く</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
@@ -806,12 +803,12 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2 天気が良ければ、ピクニックに(   )。</t>
+          <t>: もんだい2仕事が 終われば 友達と (   )。</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>1. 行きたい 2. 行く 3. 行って 4. 行かない</t>
+          <t>1. 遊ぶ 2. 学ぶ 3. 泳ぐ 4. 働く</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
@@ -830,12 +827,12 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2 暇があれば、映画を(   )。</t>
+          <t>: もんだい2天気が 良ければ ピクニックに (   )。</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>1. 見たい 2. 見る 3. 見て 4. 見ない</t>
+          <t>1. 行く 2. 帰る 3. 来る 4. 戻る</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
@@ -854,12 +851,12 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2 時間があれば、手伝いに(   )。</t>
+          <t>: もんだい2暇が あれば 映画を (   )。</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>1. 行きたい 2. 行く 3. 行って 4. 行かない</t>
+          <t>1. 見る 2. 聞く 3. 話す 4. 描く</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
@@ -878,12 +875,12 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2 勉強すれば、試験に(   )。</t>
+          <t>: もんだい2時間が あれば、手伝いに (   )。</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>1. 合格したい 2. 合格する 3. 合格して 4. 合格しない</t>
+          <t>1. 行く 2. 寝る 3. 立つ 4. 走る</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
@@ -902,12 +899,12 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2 お金があれば、旅行に(   )。</t>
+          <t>: もんだい2勉強すれば、試験に (   )。</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>1. 行きたい 2. 行く 3. 行って 4. 行かない</t>
+          <t>1. 合格する 2. 失敗する 3. 落ちる 4. 終わる</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
@@ -926,12 +923,12 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>: もんだい3 雨が降れば、試合は(   )。</t>
+          <t>: もんだい2お金が あれば、旅行に (   )。</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>1. 中止になる 2. 中止する 3. 中止で 4. 中止したい</t>
+          <t>1. 行く 2. 泊まる 3. 走る 4. 飛ぶ</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
@@ -950,17 +947,17 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>: もんだい3 この薬を飲めば、すぐに(   )。</t>
+          <t>: もんだい3雨が降れば、試合は(   )。</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>1. 治る 2. 治らない 3. 治って 4. 治りそう</t>
+          <t>1. 中止だ 2. 中止にする 3. 中止で 4. 中止になる</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr"/>
@@ -974,12 +971,12 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>: もんだい3 時間があれば、映画を(   )。</t>
+          <t>: もんだい3この薬を飲めば、すぐに(   )。</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>1. 見たい 2. 見て 3. 見ます 4. 見ない</t>
+          <t>1. 治る 2. 治らない 3. 治って 4. 治りそう</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
@@ -998,12 +995,12 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>: もんだい3 お金があれば、あの車を(   )。</t>
+          <t>: もんだい3時間があれば、映画を(   )。</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>1. 買いたい 2. 買いました 3. 買って 4. 買わない</t>
+          <t>1. 見る 2. 見て 3. 見ます 4. 見ない</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
@@ -1022,12 +1019,12 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>: もんだい3 友達が来れば、パーティーがもっと(   )。</t>
+          <t>: もんだい3お金があれば、あの車を(   )。</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>1. 楽しい 2. 楽しむ 3. 楽しんで 4. 楽しくない</t>
+          <t>1. 買う 2. 買いました 3. 買って 4. 買わない</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
@@ -1046,12 +1043,12 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>: もんだい3 天気が良ければ、ピクニックに(   )。</t>
+          <t>: もんだい3友達が来れば、パーティーがもっと(   )。</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>1. 行きたい 2. 行って 3. 行かない 4. 行こう</t>
+          <t>1. 楽しい 2. 楽しむ 3. 楽しんで 4. 楽しくない</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
@@ -1070,12 +1067,12 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>: もんだい3 もっと勉強すれば、試験に(   )。</t>
+          <t>: もんだい3天気が良ければ、ピクニックに(   )。</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>1. 合格したい 2. 合格して 3. 合格しない 4. 合格だ</t>
+          <t>1. 行く 2. 行って 3. 行かない 4. 行こう</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
@@ -1094,12 +1091,12 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>: もんだい3 静かにすれば、赤ちゃんが(   )。</t>
+          <t>: もんだい3もっと勉強すれば、試験に(   )。</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>1. 眠る 2. 眠って 3. 眠らない 4. 眠い</t>
+          <t>1. 合格する 2. 合格して 3. 合格しない 4. 合格だ</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
@@ -1118,12 +1115,12 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>: もんだい3 運動すれば、健康が(   )。</t>
+          <t>: もんだい3静かにすれば、赤ちゃんが(   )。</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>1. よくなる 2. よい 3. よくない 4. よくして</t>
+          <t>1. 眠る 2. 眠って 3. 眠らない 4. 眠い</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
@@ -1142,12 +1139,12 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>: もんだい3 早く寝れば、朝早く(   )。</t>
+          <t>: もんだい3運動すれば、健康が(   )。</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>1. 起きられる 2. 起きる 3. 起きない 4. 起きて</t>
+          <t>1. よくなる 2. よい 3. よくない 4. よくして</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
@@ -1166,17 +1163,17 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4 もし雨が降れば、ピクニックは(   )。</t>
+          <t>: もんだい3早く寝れば、朝早く(   )。</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>1. 中止したい 2. 中止しよう 3. 中止する 4. 中止した</t>
+          <t>1. 起きられる 2. 起きる 3. 起きない 4. 起きて</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr"/>
@@ -1190,12 +1187,12 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4 彼が来れば、映画を一緒に(   )。</t>
+          <t>: もんだい4もし 雨が 降れば、 ピクニックは (   )。</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>1. 見たい 2. 見たかった 3. 見たい 4. 見る</t>
+          <t>1. 中止になる 2. 中止する 3. 中止しよう 4. 中止した</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
@@ -1214,12 +1211,12 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4 この薬を飲めば、すぐに(   )。</t>
+          <t>: もんだい4彼が 来れば、 映画を 一緒に (   ).</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>1. よくなる 2. よくなりたがる 3. よくなっている 4. よくなりたい</t>
+          <t>1. 見よう 2. 見たかった 3. 見たい 4. 見る</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
@@ -1238,17 +1235,17 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4 もし試験に合格すれば、大学に(   )。</t>
+          <t>: もんだい4この薬を 飲めば、 すぐに (   ).</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>1. 行くつもりだ 2. 行きたかった 3. 行くことにした 4. 行こうと思う</t>
+          <t>1. よくなりたがる 2. よくなる 3. よくなっている 4. よくなりたい</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr"/>
@@ -1262,17 +1259,17 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4 時間があれば、あなたに手紙を(   )。</t>
+          <t>: もんだい4もし 試験に 合格すれば、 大学に (   ).</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>1. 書きたい 2. 書くことにした 3. 書く 4. 書こうと思う</t>
+          <t>1. 行くことにした 2. 行きたかった 3. 行くつもりだ 4. 行こうと思う</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr"/>
@@ -1286,17 +1283,17 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4 もし彼女が来れば、一緒に(   )。</t>
+          <t>: もんだい4時間が あれば、 あなたに 手紙を (   ).</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>1. 夕食を食べよう 2. 夕食を食べたかった 3. 夕食を食べたい 4. 夕食を食べる</t>
+          <t>1. 書く 2. 書くことにした 3. 書きたい 4. 書こうと思う</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr"/>
@@ -1310,17 +1307,17 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4 彼女が手伝えば、もっと早く(   )。</t>
+          <t>: もんだい4もし 彼女が 来れば、 一緒に (   ).</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>1. 終わらせたい 2. 終わらせよう 3. 終わらせる 4. 終わらせたかった</t>
+          <t>1. 夕食を 食べたい 2. 夕食を 食べたかった 3. 夕食を 食べよう 4. 夕食を 食べる</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr"/>
@@ -1334,17 +1331,17 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4 もしお金があれば、新しいスマホを(   )。</t>
+          <t>: もんだい4彼女が 手伝えば、 もっと 早く (   ).</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>1. 買いたい 2. 買おう 3. 買う 4. 買うことにした</t>
+          <t>1. 終わらせたかった 2. 終わらせたい 3. 終わらせよう 4. 終わらせる</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr"/>
@@ -1358,12 +1355,12 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4 もっと練習すれば、試合に(   )。</t>
+          <t>: もんだい4もし お金が あれば、 新しいスマホを (   ).</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>1. 勝てる 2. 勝ちたい 3. 勝ちたがる 4. 勝ちそうだ</t>
+          <t>1. 買いたい 2. 買う 3. 買おう 4. 買うことにした</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
@@ -1382,17 +1379,17 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4 これをやれば、すぐに終わると(   )。</t>
+          <t>: もんだい4もっと 練習すれば、 試合に (   )。</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>1. 思う 2. 思った 3. 思いたい 4. 思っている</t>
+          <t>1. 勝ちたがる 2. 勝てる 3. 勝ちたい 4. 勝ちそうだ</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr"/>
@@ -1406,17 +1403,17 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5 この本は面白いが、あの本(   )面白くない。</t>
+          <t>: もんだい4これを やれば、 すぐに 終わると (   )。</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>1. ほど 2. なら 3. しか 4. ばかり</t>
+          <t>1. 思った 2. 思っている 3. 思いたい 4. 思う</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr"/>
@@ -1430,12 +1427,12 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5 この道をまっすぐ行けば、駅に着きますよ。</t>
+          <t>: もんだい5この本は面白いが、あの本 (   ) 面白くない。</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>1. なら 2. ば 3. ほど 4. から</t>
+          <t>1. ほど 2. なら 3. しか 4. ばかり</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
@@ -1454,17 +1451,17 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5 雨が降らなければ、ピクニックに行きます。</t>
+          <t>: もんだい5この道をまっすぐ(   )駅に着きますよ。</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>1. ほど 2. ば 3. から 4. まで</t>
+          <t>1. なら 2. ば 3. ほど 4. まで</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr"/>
@@ -1478,12 +1475,12 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5 宿題を終わらせれば、遊びに行ってもいいです。</t>
+          <t>: もんだい5雨が降らなければ(   )ピクニックに行きます。</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>1. から 2. ば 3. ほど 4. だけ</t>
+          <t>1. ほど 2. ば 3. から 4. まで</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
@@ -1502,12 +1499,12 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5 この映画は怖いが、あの映画(   )怖くない。</t>
+          <t>: もんだい5宿題を終わらせたら(   )遊びに行ってもいいです。</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>1. ほど 2. から 3. なら 4. まで</t>
+          <t>1. から 2. ば 3. ほど 4. だけ</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
@@ -1526,17 +1523,17 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5 たくさん練習すれば、上手になります。</t>
+          <t>: もんだい5この映画は怖いが、あの映画 (   ) 怖くない。</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>1. なら 2. ば 3. ほど 4. から</t>
+          <t>1. ほど 2. から 3. なら 4. まで</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr"/>
@@ -1550,17 +1547,17 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5 お金があれば、旅行に行きたいです。</t>
+          <t>: もんだい5たくさん練習すれば(   )上手になります。</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>1. ば 2. から 3. ほど 4. しか</t>
+          <t>1. なら 2. ば 3. ほど 4. から</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr"/>
@@ -1574,12 +1571,12 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5 早く寝れば、明日元気になります。</t>
+          <t>: もんだい5お金があれば(   )旅行に行きたいです。</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>1. ば 2. から 3. ほど 4. だけ</t>
+          <t>1. ば 2. から 3. ほど 4. しか</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
@@ -1598,12 +1595,12 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5 彼は賢いが、彼女(   )賢くない。</t>
+          <t>: もんだい5早く寝たら(   )明日元気になります。</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>1. ほど 2. ば 3. から 4. まで</t>
+          <t>1. ば 2. から 3. ほど 4. だけ</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
@@ -1622,12 +1619,12 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5 勉強すれば、するほど、試験が簡単になります。</t>
+          <t>: もんだい5彼は賢いが、彼女 (   ) 賢くない。</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>1. なら 2. ば 3. ほど 4. から</t>
+          <t>1. ほど 2. ば 3. から 4. まで</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
@@ -1646,17 +1643,17 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6 A:「雨が降れば、」 B:「(   )。」</t>
+          <t>: もんだい5勉強するほど(   )試験が難しくなります。</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>1. 試合は中止になる 2. 試合が中止になる 3. 試合を中止になる 4. 試合は中止にする</t>
+          <t>1. なら 2. ば 3. ほど 4. から</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr"/>
@@ -1670,17 +1667,17 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6 A:「この本、面白ければ、」 B:「(   )。」</t>
+          <t>: もんだい6A:「雨が降れば、」 B:「(   )。 」</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>1. 私に貸してくれませんか 2. 私に貸してください 3. 私に貸してもいいですか 4. 私に貸していただけますか</t>
+          <t>1. 試合は中止です 2. 試合が中止です 3. 試合を中止です 4. 試合は中止にします</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr"/>
@@ -1694,17 +1691,17 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6 A:「時間があれば、」 B:「(   )。」</t>
+          <t>: もんだい6A:「この本、面白ければ、」 B:「(   )。 」</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>1. 一緒に行きませんか 2. 一緒に行ってもいいですか 3. 一緒に行ってください 4. 一緒に行ってほしいです</t>
+          <t>1. 私に貸してください 2. 私に貸してもいいですか 3. 私に貸してくれませんか 4. 私に貸していただけますか</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr"/>
@@ -1718,12 +1715,12 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6 A:「いい天気なら、」 B:「(   )。」</t>
+          <t>: もんだい6A:「時間があれば、」 B:「(   )。 」</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>1. 山に登りましょう 2. 山に登ります 3. 山に登ってください 4. 山に登りたいです</t>
+          <t>1. 一緒に行きませんか 2. 一緒に行ってもいいですか 3. 一緒に行ってください 4. 一緒に行ってほしいです</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
@@ -1742,12 +1739,12 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6 A:「もし暇があれば、」 B:「(   )。」</t>
+          <t>: もんだい6A:「いい天気なら、」 B:「(   )。 」</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>1. 映画を見に行きましょうか 2. 映画を見に行ってください 3. 映画を見に行きますか 4. 映画を見に行ってもいいですか</t>
+          <t>1. 山に登りましょう 2. 山に登ります 3. 山に登ってください 4. 山に登りたいです</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
@@ -1766,12 +1763,12 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6 A:「風邪を引いたら、」 B:「(   )。」</t>
+          <t>: もんだい6A:「もし暇があれば、」 B:「(   )。 」</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>1. 早く寝たほうがいいです 2. 早く寝ますか 3. 早く寝てください 4. 早く寝たらどうですか</t>
+          <t>1. 映画を見に行きましょうか 2. 映画を見に行ってください 3. 映画を見に行きますか 4. 映画を見に行ってもいいですか</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
@@ -1790,12 +1787,12 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6 A:「道が分からなければ、」 B:「(   )。」</t>
+          <t>: もんだい6A:「風邪を引いたら、」 B:「(   )。 」</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>1. 誰かに聞いてください 2. 誰かに聞きませんか 3. 誰かに聞いてもいいですか 4. 誰かに聞くといいです</t>
+          <t>1. 早く寝たほうがいいです 2. 早く寝ますか 3. 早く寝てください 4. 早く寝たらどうですか</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr">
@@ -1814,12 +1811,12 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6 A:「お金があれば、」 B:「(   )。」</t>
+          <t>: もんだい6A:「道が分からなければ、」 B:「(   )。 」</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>1. 新しい車を買いたいです 2. 新しい車を買いますか 3. 新しい車を買ってください 4. 新しい車を買ったらいいです</t>
+          <t>1. 誰かに聞いてください 2. 誰かに聞きませんか 3. 誰かに聞いてもいいですか 4. 誰かに聞くといいです</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
@@ -1838,12 +1835,12 @@
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6 A:「疲れたら、」 B:「(   )。」</t>
+          <t>: もんだい6A:「お金があれば、」 B:「(   )。 」</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>1. 休んだほうがいいです 2. 休んでください 3. 休みましょう 4. 休んでもいいですか</t>
+          <t>1. 新しい車を買いたいです 2. 新しい車を買いますか 3. 新しい車を買ってください 4. 新しい車を買ったらいいです</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
@@ -1862,12 +1859,12 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6 A:「彼が来れば、」 B:「(   )。」</t>
+          <t>: もんだい6A:「疲れたら、」 B:「(   )。 」</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>1. パーティーを始めましょう 2. パーティーを始めます 3. パーティーを始めてください 4. パーティーを始めてもいいですか</t>
+          <t>1. 休んだほうがいいです 2. 休んでください 3. 休みましょう 4. 休んでもいいですか</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
@@ -1886,17 +1883,17 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7 雨が降れば、ピクニックは(   )。</t>
+          <t>: もんだい6A:「彼が来れば、」 B:「(   )。 」</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>1. 中止になる 2. 中止にしよう 3. 中止する 4. 中止できる</t>
+          <t>1. パーティーを始めます 2. パーティーを始めましょう 3. パーティーを始めてください 4. パーティーを始めてもいいですか</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr"/>
@@ -1910,17 +1907,17 @@
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7 あの映画は面白ければ、(   )。</t>
+          <t>: もんだい7雨が降れば、ピクニックは(   )。</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>1. 見たくなる 2. 見ることになる 3. 見なければならない 4. 見よう</t>
+          <t>1. 中止にしよう 2. 中止になる 3. 中止にする 4. 中止できる</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr"/>
@@ -1934,17 +1931,17 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7 勉強すれば、テストに(   )。</t>
+          <t>: もんだい7あの映画は面白ければ、(   )。</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>1. 合格できる 2. 合格する 3. 合格しない 4. 合格にならない</t>
+          <t>1. 見ることになる 2. 見たくなる 3. 見なければならない 4. 見よう</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr"/>
@@ -1958,12 +1955,12 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7 このボタンを押せば、(   )。</t>
+          <t>: もんだい7勉強すれば、テストに(   )。</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>1. ドアが開く 2. ドアが開ける 3. ドアを開ける 4. ドアを開かない</t>
+          <t>1. 合格できる 2. 合格する 3. 合格しない 4. 合格にならない</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
@@ -1982,17 +1979,17 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7 この薬を飲めば、(   )。</t>
+          <t>: もんだい7このボタンを押せば、(   )。</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>1. よくなるかもしれない 2. よくならないかもしれない 3. よくなることにした 4. よくなるつもりだ</t>
+          <t>1. ドアが開ける 2. ドアが開く 3. ドアを開ける 4. ドアを開かない</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr"/>
@@ -2006,12 +2003,12 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7 時間があれば、(   )。</t>
+          <t>: もんだい7この薬を飲めば、(   )。</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>1. 映画を見よう 2. 映画を見たい 3. 映画を見ようと思う 4. 映画を見てもいい</t>
+          <t>1. よくなるかもしれない 2. よくならないかもしれない 3. よくなることにした 4. よくなるつもりだ</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
@@ -2030,17 +2027,17 @@
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7 家に帰れば、(   )。</t>
+          <t>: もんだい7時間があれば、(   )。</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>1. リラックスできる 2. リラックスしなければならない 3. リラックスしている 4. リラックスしたい</t>
+          <t>1. 映画を見たい 2. 映画を見よう 3. 映画を見ようと思う 4. 映画を見てもいい</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr"/>
@@ -2054,12 +2051,12 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7 お金があれば、(   )。</t>
+          <t>: もんだい7家に帰れば、(   )。</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>1. 旅行に行こう 2. 旅行に行かない 3. 旅行に行くことになった 4. 旅行に行った</t>
+          <t>1. リラックスできる 2. リラックスしなければならない 3. リラックスしている 4. リラックスしたい</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
@@ -2078,12 +2075,12 @@
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7 彼が来れば、(   )。</t>
+          <t>: もんだい7お金があれば、(   )。</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>1. パーティーが始まる 2. パーティーを始める 3. パーティーが始める 4. パーティーを始まる</t>
+          <t>1. 旅行に行こう 2. 旅行に行かない 3. 旅行に行くことになった 4. 旅行に行った</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
@@ -2102,17 +2099,17 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7 この本を読めば、(   )。</t>
+          <t>: もんだい7彼が来れば、(   )。</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>1. 話がわかる 2. 話をわかる 3. 話がわからない 4. 話をわからない</t>
+          <t>1. パーティーが始める 2. パーティーを始める 3. パーティーが始まる 4. パーティーを始まる</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr"/>
@@ -2126,17 +2123,17 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>: もんだい8 雨が降れば、道が(   )なる。</t>
+          <t>: もんだい7この本を読めば、(   )。</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>1. みたいに 2. ように 3. ほど 4. らしく</t>
+          <t>1. 話がわかる 2. 話をわかる 3. 話がわからない 4. 話をわからない</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr"/>
@@ -2150,17 +2147,17 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>: もんだい8 その子供は、大人の(   )賢い。</t>
+          <t>: もんだい8雨が降れば、道が(   )なる。</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>1. ように 2. ほどに 3. らしく 4. みたい</t>
+          <t>1. みたいに 2. ように 3. ほど 4. らしく</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr"/>
@@ -2174,17 +2171,17 @@
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>: もんだい8 彼女が笑えば、太陽の(   )明るくなる。</t>
+          <t>: もんだい8その子供は、大人の(   )賢い。</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>1. ほどに 2. みたいに 3. ように 4. らしく</t>
+          <t>1. ように 2. ほどに 3. らしく 4. みたい</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr"/>
@@ -2198,17 +2195,17 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>: もんだい8 もし疲れれば、猫の(   )眠ることができる。</t>
+          <t>: もんだい8彼女が笑えば、太陽の(   )明るくなる。</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>1. ように 2. ほどに 3. みたいに 4. らしく</t>
+          <t>1. ほどに 2. みたいに 3. ように 4. らしく</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr"/>
@@ -2222,12 +2219,12 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>: もんだい8 彼が来れば、すべてが(   )解決する。</t>
+          <t>: もんだい8もし疲れれば、猫の(   )眠ることができる。</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>1. らしく 2. みたいに 3. ように 4. ほど</t>
+          <t>1. ように 2. ほどに 3. みたいに 4. らしく</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
@@ -2246,12 +2243,12 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>: もんだい8 この歌を聴けば、昔の(   )思い出す。</t>
+          <t>: もんだい8彼が来れば、すべてが(   )解決する。</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>1. ほどに 2. みたいに 3. ように 4. らしく</t>
+          <t>1. らしく 2. みたいに 3. ように 4. ほど</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
@@ -2270,17 +2267,17 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>: もんだい8 彼女が手伝えば、仕事が(   )早く終わる。</t>
+          <t>: もんだい8この歌を聴けば、昔の(   )思い出す。</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>1. ように 2. みたいに 3. ほどに 4. らしく</t>
+          <t>1. ほどに 2. みたいに 3. ように 4. らしく</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr"/>
@@ -2294,17 +2291,17 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>: もんだい8 あの映画を見れば、夢の(   )感じる。</t>
+          <t>: もんだい8彼女が手伝えば、仕事が(   )早く終わる。</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>1. ように 2. ほどに 3. らしく 4. みたいに</t>
+          <t>1. ように 2. みたいに 3. ほどに 4. らしく</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr"/>
@@ -2318,17 +2315,17 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>: もんだい8 彼が説明すれば、子供でも(   )わかる。</t>
+          <t>: もんだい8あの映画を見れば、夢の(   )感じる。</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>1. ように 2. ほどに 3. みたいに 4. らしく</t>
+          <t>1. ように 2. ほどに 3. らしく 4. みたいに</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr"/>
@@ -2342,25 +2339,49 @@
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>: もんだい8 この薬を飲めば、魔法の(   )効く。</t>
+          <t>: もんだい8彼が説明すれば、子供でも(   )わかる。</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>1. みたいに 2. ように 3. ほどに 4. らしく</t>
+          <t>1. ように 2. ほどに 3. みたいに 4. らしく</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr"/>
       <c r="F80" s="1" t="inlineStr"/>
     </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>: もんだい8この薬を飲めば、魔法の(   )効く。</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>1. みたいに 2. ように 3. ほどに 4. らしく</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E81" s="1" t="inlineStr"/>
+      <c r="F81" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E2:E80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"High_Q,Low_Q,Drop,Minor changes"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/revised_shatin/qwen3-next-80b-a3b-thinking/test_grammar_2_['No. 91_～ば〈条件(じょうけん)〉 ']_revised_revised.xlsx
+++ b/docs/revised_shatin/qwen3-next-80b-a3b-thinking/test_grammar_2_['No. 91_～ば〈条件(じょうけん)〉 ']_revised_revised.xlsx
@@ -1187,17 +1187,17 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4もし 雨が 降れば、 ピクニックは (   )。</t>
+          <t>: もんだい4もし 雨が 降れば、 ピクニックは (   ).</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>1. 中止になる 2. 中止する 3. 中止しよう 4. 中止した</t>
+          <t>1. 中止したい 2. 中止する 3. 中止しよう 4. 中止した</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4これを やれば、 すぐに 終わると (   )。</t>
+          <t>: もんだい4これを やれば、 すぐに 終わると (   ).</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr"/>
@@ -1451,17 +1451,17 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5この道をまっすぐ(   )駅に着きますよ。</t>
+          <t>: もんだい5この道をまっすぐ行け (   ) 駅に着きますよ。</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>1. なら 2. ば 3. ほど 4. まで</t>
+          <t>1. なら 2. ば 3. ほど 4. から</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr"/>
@@ -1475,17 +1475,17 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5雨が降らなければ(   )ピクニックに行きます。</t>
+          <t>: もんだい5雨が降らなけれ(   )ピクニックに行きます。</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>1. ほど 2. ば 3. から 4. まで</t>
+          <t>1. ば 2. ほど 3. から 4. まで</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr"/>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5宿題を終わらせたら(   )遊びに行ってもいいです。</t>
+          <t>: もんだい5宿題を終わらせ(   )遊びに行ってもいいです。</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>1. から 2. ば 3. ほど 4. だけ</t>
+          <t>1. たら 2. ば 3. なら 4. ても</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr"/>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>1. なら 2. ば 3. ほど 4. から</t>
+          <t>1. ほど 2. なら 3. たって 4. ても</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr"/>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>1. ば 2. から 3. ほど 4. しか</t>
+          <t>1. きっと 2. ぜひ 3. ぜひ 4. ぜひ</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5早く寝たら(   )明日元気になります。</t>
+          <t>: もんだい5早く寝れば(   )明日元気になります。</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>1. ば 2. から 3. ほど 4. だけ</t>
+          <t>1. きっと 2. ぜひ 3. ぜひ 4. ぜひ</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr"/>
@@ -1643,17 +1643,17 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5勉強するほど(   )試験が難しくなります。</t>
+          <t>: もんだい5勉強すればするほど、試験が(   )。</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>1. なら 2. ば 3. ほど 4. から</t>
+          <t>1. 簡単になる 2. 難しくなる 3. 早くなる 4. 大変になる</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr"/>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr"/>
@@ -1691,17 +1691,17 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6A:「この本、面白ければ、」 B:「(   )。 」</t>
+          <t>: もんだい6A:「この本、面白ければ、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>1. 私に貸してください 2. 私に貸してもいいですか 3. 私に貸してくれませんか 4. 私に貸していただけますか</t>
+          <t>1. 私に貸してください 2. 私に貸してもいいですか 3. 私に貸していただけますか 4. 私に貸してくれませんか</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr"/>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6A:「時間があれば、」 B:「(   )。 」</t>
+          <t>: もんだい6A:「時間があれば、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>1. 一緒に行きませんか 2. 一緒に行ってもいいですか 3. 一緒に行ってください 4. 一緒に行ってほしいです</t>
+          <t>1. 一緒に行きましょう 2. 一緒に行ってもいいですか 3. 一緒に行ってください 4. 一緒に行ってほしいです</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6A:「いい天気なら、」 B:「(   )。 」</t>
+          <t>: もんだい6A:「いい天気なら、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6A:「もし暇があれば、」 B:「(   )。 」</t>
+          <t>: もんだい6A:「もし暇があれば、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6A:「風邪を引いたら、」 B:「(   )。 」</t>
+          <t>: もんだい6A:「風邪を引いたら、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6A:「道が分からなければ、」 B:「(   )。 」</t>
+          <t>: もんだい6A:「道が分からなければ、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6A:「お金があれば、」 B:「(   )。 」</t>
+          <t>: もんだい6A:「お金があれば、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6A:「疲れたら、」 B:「(   )。 」</t>
+          <t>: もんだい6A:「疲れたら、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6A:「彼が来れば、」 B:「(   )。 」</t>
+          <t>: もんだい6A:「彼が来れば、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -1984,12 +1984,12 @@
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>1. ドアが開ける 2. ドアが開く 3. ドアを開ける 4. ドアを開かない</t>
+          <t>1. ドアが開く 2. ドアが開ける 3. ドアを開ける 4. ドアを開かない</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr"/>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr"/>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr"/>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E81" s="1" t="inlineStr"/>
